--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_ALCOBENDAS C.B..xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_ALCOBENDAS C.B..xlsx
@@ -565,13 +565,13 @@
         <v>18</v>
       </c>
       <c r="D2" t="n">
-        <v>56.78360000000001</v>
+        <v>51.2556</v>
       </c>
       <c r="E2" t="n">
-        <v>37.82380000000001</v>
+        <v>35.5901</v>
       </c>
       <c r="F2" t="n">
-        <v>18.9602</v>
+        <v>15.6655</v>
       </c>
       <c r="G2" t="n">
         <v>31.2875</v>
@@ -610,13 +610,13 @@
         <v>36.6848</v>
       </c>
       <c r="S2" t="n">
-        <v>16.948</v>
+        <v>11.4197</v>
       </c>
       <c r="T2" t="n">
-        <v>6.8308</v>
+        <v>4.597</v>
       </c>
       <c r="U2" t="n">
-        <v>10.1173</v>
+        <v>6.8226</v>
       </c>
       <c r="V2" t="n">
         <v>14.9199</v>
@@ -643,13 +643,13 @@
         <v>26</v>
       </c>
       <c r="D3" t="n">
-        <v>31.9562</v>
+        <v>21.543</v>
       </c>
       <c r="E3" t="n">
-        <v>20.0639</v>
+        <v>14.6172</v>
       </c>
       <c r="F3" t="n">
-        <v>11.8923</v>
+        <v>6.925699999999999</v>
       </c>
       <c r="G3" t="n">
         <v>4.1259</v>
@@ -688,13 +688,13 @@
         <v>39.0015</v>
       </c>
       <c r="S3" t="n">
-        <v>19.6687</v>
+        <v>9.254799999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>6.6908</v>
+        <v>1.2442</v>
       </c>
       <c r="U3" t="n">
-        <v>12.9778</v>
+        <v>8.010999999999999</v>
       </c>
       <c r="V3" t="n">
         <v>9.7065</v>
@@ -721,13 +721,13 @@
         <v>26</v>
       </c>
       <c r="D4" t="n">
-        <v>9.567</v>
+        <v>19.8148</v>
       </c>
       <c r="E4" t="n">
-        <v>18.6804</v>
+        <v>25.5823</v>
       </c>
       <c r="F4" t="n">
-        <v>-9.113199999999999</v>
+        <v>-5.767</v>
       </c>
       <c r="G4" t="n">
         <v>13.4709</v>
@@ -766,13 +766,13 @@
         <v>27.4173</v>
       </c>
       <c r="S4" t="n">
-        <v>-8.8208</v>
+        <v>1.427</v>
       </c>
       <c r="T4" t="n">
-        <v>-6.985</v>
+        <v>-0.0830000000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.8357</v>
+        <v>1.5104</v>
       </c>
       <c r="V4" t="n">
         <v>-3.771699999999999</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. RELAÑO LOPEZ</t>
+          <t>A. MARÍN REYES</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="D5" t="n">
-        <v>8.653499999999999</v>
+        <v>16.5692</v>
       </c>
       <c r="E5" t="n">
-        <v>1.652799999999999</v>
+        <v>-6.355500000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>7.000599999999999</v>
+        <v>22.9251</v>
       </c>
       <c r="G5" t="n">
-        <v>10.0291</v>
+        <v>12.8275</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3904999999999994</v>
+        <v>6.424900000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>9.638299999999999</v>
+        <v>6.4028</v>
       </c>
       <c r="J5" t="n">
-        <v>15.2681</v>
+        <v>15.42</v>
       </c>
       <c r="K5" t="n">
-        <v>5.779999999999999</v>
+        <v>7.678100000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>9.488299999999999</v>
+        <v>7.742199999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>-5.2387</v>
+        <v>-2.5926</v>
       </c>
       <c r="N5" t="n">
-        <v>-5.3892</v>
+        <v>-1.2533</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1503000000000004</v>
+        <v>-1.3395</v>
       </c>
       <c r="P5" t="n">
-        <v>-5.020099999999999</v>
+        <v>-4.634</v>
       </c>
       <c r="Q5" t="n">
-        <v>-30.3136</v>
+        <v>-32.2441</v>
       </c>
       <c r="R5" t="n">
-        <v>25.2933</v>
+        <v>27.6101</v>
       </c>
       <c r="S5" t="n">
-        <v>13.2189</v>
+        <v>-2.0478</v>
       </c>
       <c r="T5" t="n">
-        <v>5.2613</v>
+        <v>-6.178</v>
       </c>
       <c r="U5" t="n">
-        <v>7.9576</v>
+        <v>4.1302</v>
       </c>
       <c r="V5" t="n">
-        <v>-9.574400000000001</v>
+        <v>10.4235</v>
       </c>
       <c r="W5" t="n">
-        <v>11.4373</v>
+        <v>16.6462</v>
       </c>
       <c r="X5" t="n">
-        <v>-21.0116</v>
+        <v>-6.2229</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. MARÍN REYES</t>
+          <t>A. GUERRERO PAEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D6" t="n">
-        <v>7.8326</v>
+        <v>12.2305</v>
       </c>
       <c r="E6" t="n">
-        <v>-12.1269</v>
+        <v>9.113099999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>19.9596</v>
+        <v>3.1174</v>
       </c>
       <c r="G6" t="n">
-        <v>12.8275</v>
+        <v>4.064300000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>6.424900000000001</v>
+        <v>-0.2725999999999996</v>
       </c>
       <c r="I6" t="n">
-        <v>6.4028</v>
+        <v>4.336900000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>15.42</v>
+        <v>17.6913</v>
       </c>
       <c r="K6" t="n">
-        <v>7.678100000000001</v>
+        <v>7.118600000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>7.742199999999999</v>
+        <v>10.5726</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.5926</v>
+        <v>-13.6267</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.2533</v>
+        <v>-7.391</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.3395</v>
+        <v>-6.236</v>
       </c>
       <c r="P6" t="n">
-        <v>-4.634</v>
+        <v>5.7924</v>
       </c>
       <c r="Q6" t="n">
-        <v>-32.2441</v>
+        <v>-16.2188</v>
       </c>
       <c r="R6" t="n">
-        <v>27.6101</v>
+        <v>22.0109</v>
       </c>
       <c r="S6" t="n">
-        <v>-10.7846</v>
+        <v>2.3029</v>
       </c>
       <c r="T6" t="n">
-        <v>-11.9492</v>
+        <v>-1.4822</v>
       </c>
       <c r="U6" t="n">
-        <v>1.1648</v>
+        <v>3.785</v>
       </c>
       <c r="V6" t="n">
-        <v>10.4235</v>
+        <v>0.07070000000000022</v>
       </c>
       <c r="W6" t="n">
-        <v>16.6462</v>
+        <v>9.122399999999999</v>
       </c>
       <c r="X6" t="n">
-        <v>-6.2229</v>
+        <v>-9.0518</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Í. MATEO CASTAÑO</t>
+          <t>A. RELAÑO LOPEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>26</v>
       </c>
       <c r="D7" t="n">
-        <v>3.354699999999999</v>
+        <v>3.5032</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4087999999999998</v>
+        <v>-1.2011</v>
       </c>
       <c r="F7" t="n">
-        <v>2.9459</v>
+        <v>4.7044</v>
       </c>
       <c r="G7" t="n">
-        <v>-13.4105</v>
+        <v>10.0291</v>
       </c>
       <c r="H7" t="n">
-        <v>-10.271</v>
+        <v>0.3904999999999994</v>
       </c>
       <c r="I7" t="n">
-        <v>-3.1401</v>
+        <v>9.638299999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>2.1139</v>
+        <v>15.2681</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.2548999999999995</v>
+        <v>5.779999999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>2.3684</v>
+        <v>9.488299999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>-15.5245</v>
+        <v>-5.2387</v>
       </c>
       <c r="N7" t="n">
-        <v>-10.0163</v>
+        <v>-5.3892</v>
       </c>
       <c r="O7" t="n">
-        <v>-5.5082</v>
+        <v>0.1503000000000004</v>
       </c>
       <c r="P7" t="n">
-        <v>16.025</v>
+        <v>-5.020099999999999</v>
       </c>
       <c r="Q7" t="n">
-        <v>-18.5357</v>
+        <v>-30.3136</v>
       </c>
       <c r="R7" t="n">
-        <v>34.5606</v>
+        <v>25.2933</v>
       </c>
       <c r="S7" t="n">
-        <v>9.4481</v>
+        <v>8.068300000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>8.292</v>
+        <v>2.407</v>
       </c>
       <c r="U7" t="n">
-        <v>1.1564</v>
+        <v>5.6613</v>
       </c>
       <c r="V7" t="n">
-        <v>-8.708</v>
+        <v>-9.574400000000001</v>
       </c>
       <c r="W7" t="n">
-        <v>8.538399999999999</v>
+        <v>11.4373</v>
       </c>
       <c r="X7" t="n">
-        <v>-17.2465</v>
+        <v>-21.0116</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. GUERRERO PAEZ</t>
+          <t>D. BRAVO TRIGO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>1.265899999999999</v>
+        <v>1.3978</v>
       </c>
       <c r="E8" t="n">
-        <v>1.790599999999999</v>
+        <v>-1.6533</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5243999999999996</v>
+        <v>3.0513</v>
       </c>
       <c r="G8" t="n">
-        <v>4.064300000000001</v>
+        <v>1.18</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2725999999999996</v>
+        <v>2.6065</v>
       </c>
       <c r="I8" t="n">
-        <v>4.336900000000001</v>
+        <v>-1.4264</v>
       </c>
       <c r="J8" t="n">
-        <v>17.6913</v>
+        <v>0.3261</v>
       </c>
       <c r="K8" t="n">
-        <v>7.118600000000001</v>
+        <v>1.7796</v>
       </c>
       <c r="L8" t="n">
-        <v>10.5726</v>
+        <v>-1.4535</v>
       </c>
       <c r="M8" t="n">
-        <v>-13.6267</v>
+        <v>0.8539000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>-7.391</v>
+        <v>0.8269000000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>-6.236</v>
+        <v>0.02720000000000006</v>
       </c>
       <c r="P8" t="n">
-        <v>5.7924</v>
+        <v>0.3862000000000001</v>
       </c>
       <c r="Q8" t="n">
-        <v>-16.2188</v>
+        <v>-1.9308</v>
       </c>
       <c r="R8" t="n">
-        <v>22.0109</v>
+        <v>2.317</v>
       </c>
       <c r="S8" t="n">
-        <v>-8.661300000000001</v>
+        <v>0.1173</v>
       </c>
       <c r="T8" t="n">
-        <v>-8.8048</v>
+        <v>-0.04850000000000002</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1433</v>
+        <v>0.1659</v>
       </c>
       <c r="V8" t="n">
-        <v>0.07070000000000022</v>
+        <v>-0.2856</v>
       </c>
       <c r="W8" t="n">
-        <v>9.122399999999999</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-9.0518</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. BRAVO TRIGO</t>
+          <t>Í. MATEO CASTAÑO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,70 +1108,70 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7731</v>
+        <v>1.3186</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.6051</v>
+        <v>-4.258900000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>2.3781</v>
+        <v>5.5778</v>
       </c>
       <c r="G9" t="n">
-        <v>1.18</v>
+        <v>-13.4105</v>
       </c>
       <c r="H9" t="n">
-        <v>2.6065</v>
+        <v>-10.271</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.4264</v>
+        <v>-3.1401</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3261</v>
+        <v>2.1139</v>
       </c>
       <c r="K9" t="n">
-        <v>1.7796</v>
+        <v>-0.2548999999999995</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.4535</v>
+        <v>2.3684</v>
       </c>
       <c r="M9" t="n">
-        <v>0.8539000000000001</v>
+        <v>-15.5245</v>
       </c>
       <c r="N9" t="n">
-        <v>0.8269000000000001</v>
+        <v>-10.0163</v>
       </c>
       <c r="O9" t="n">
-        <v>0.02720000000000006</v>
+        <v>-5.5082</v>
       </c>
       <c r="P9" t="n">
-        <v>0.3862000000000001</v>
+        <v>16.025</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.9308</v>
+        <v>-18.5357</v>
       </c>
       <c r="R9" t="n">
-        <v>2.317</v>
+        <v>34.5606</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5075999999999999</v>
+        <v>7.412</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0002999999999999947</v>
+        <v>3.6242</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5071</v>
+        <v>3.788</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.2856</v>
+        <v>-8.708</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>8.538399999999999</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2856</v>
+        <v>-17.2465</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.8602</v>
+        <v>-0.8354</v>
       </c>
       <c r="E10" t="n">
         <v>-0.18</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6802</v>
+        <v>-0.6553</v>
       </c>
       <c r="G10" t="n">
         <v>-0.7112000000000001</v>
@@ -1234,13 +1234,13 @@
         <v>0.1931</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3421</v>
+        <v>-0.3172</v>
       </c>
       <c r="T10" t="n">
         <v>-0.2207</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1213</v>
+        <v>-0.0965</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.629</v>
+        <v>-1.9533</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.256</v>
+        <v>-2.5803</v>
       </c>
       <c r="F11" t="n">
         <v>0.627</v>
@@ -1312,10 +1312,10 @@
         <v>1.1585</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1654</v>
+        <v>0.5103</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3036</v>
+        <v>0.3722</v>
       </c>
       <c r="U11" t="n">
         <v>0.1381</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>R. TERRATS MADRID</t>
+          <t>N. MARTINEZ DE SAN VICENTE MARTIN</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.732099999999999</v>
+        <v>-6.7795</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.722300000000001</v>
+        <v>-6.695</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9906000000000006</v>
+        <v>-0.08460000000000023</v>
       </c>
       <c r="G12" t="n">
-        <v>3.838000000000001</v>
+        <v>-5.0446</v>
       </c>
       <c r="H12" t="n">
-        <v>1.4401</v>
+        <v>-3.0823</v>
       </c>
       <c r="I12" t="n">
-        <v>2.397899999999999</v>
+        <v>-1.9623</v>
       </c>
       <c r="J12" t="n">
-        <v>14.5829</v>
+        <v>-3.7251</v>
       </c>
       <c r="K12" t="n">
-        <v>12.7629</v>
+        <v>-2.3913</v>
       </c>
       <c r="L12" t="n">
-        <v>1.8204</v>
+        <v>-1.3337</v>
       </c>
       <c r="M12" t="n">
-        <v>-10.745</v>
+        <v>-1.3195</v>
       </c>
       <c r="N12" t="n">
-        <v>-11.3224</v>
+        <v>-0.6909999999999999</v>
       </c>
       <c r="O12" t="n">
-        <v>0.5773999999999999</v>
+        <v>-0.6286</v>
       </c>
       <c r="P12" t="n">
-        <v>-14.4807</v>
+        <v>-0.7722</v>
       </c>
       <c r="Q12" t="n">
-        <v>-38.2298</v>
+        <v>-2.8962</v>
       </c>
       <c r="R12" t="n">
-        <v>23.7487</v>
+        <v>2.124</v>
       </c>
       <c r="S12" t="n">
-        <v>18.5126</v>
+        <v>-0.6343000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>13.755</v>
+        <v>-0.3594000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>4.7576</v>
+        <v>-0.2749</v>
       </c>
       <c r="V12" t="n">
-        <v>-12.6018</v>
+        <v>-0.3282</v>
       </c>
       <c r="W12" t="n">
-        <v>4.1689</v>
+        <v>0.2856</v>
       </c>
       <c r="X12" t="n">
-        <v>-16.7708</v>
+        <v>-0.6138</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>N. MARTINEZ DE SAN VICENTE MARTIN</t>
+          <t>A. BARBEITO RUIZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.2925</v>
+        <v>-10.9975</v>
       </c>
       <c r="E13" t="n">
-        <v>-7.1086</v>
+        <v>-9.966100000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.1838000000000002</v>
+        <v>-1.031199999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>-5.0446</v>
+        <v>-1.6784</v>
       </c>
       <c r="H13" t="n">
-        <v>-3.0823</v>
+        <v>4.9278</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.9623</v>
+        <v>-6.6059</v>
       </c>
       <c r="J13" t="n">
-        <v>-3.7251</v>
+        <v>3.793</v>
       </c>
       <c r="K13" t="n">
-        <v>-2.3913</v>
+        <v>6.385300000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.3337</v>
+        <v>-2.5923</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.3195</v>
+        <v>-5.471299999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.6909999999999999</v>
+        <v>-1.4579</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.6286</v>
+        <v>-4.0136</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.7722</v>
+        <v>2.5098</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.8962</v>
+        <v>-17.3772</v>
       </c>
       <c r="R13" t="n">
-        <v>2.124</v>
+        <v>19.8869</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.1473</v>
+        <v>-1.5789</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7730999999999999</v>
+        <v>-0.5084</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3743</v>
+        <v>-1.0706</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.3282</v>
+        <v>-10.2505</v>
       </c>
       <c r="W13" t="n">
-        <v>0.2856</v>
+        <v>4.1264</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.6138</v>
+        <v>-14.3769</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. SANTOLARIA MARTIN</t>
+          <t>R. TERRATS MADRID</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D14" t="n">
-        <v>-9.645900000000001</v>
+        <v>-13.8806</v>
       </c>
       <c r="E14" t="n">
-        <v>3.355</v>
+        <v>-13.8716</v>
       </c>
       <c r="F14" t="n">
-        <v>-13.0008</v>
+        <v>-0.008599999999999774</v>
       </c>
       <c r="G14" t="n">
-        <v>2.622400000000001</v>
+        <v>3.838000000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>1.6869</v>
+        <v>1.4401</v>
       </c>
       <c r="I14" t="n">
-        <v>0.9354000000000001</v>
+        <v>2.397899999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>8.1434</v>
+        <v>14.5829</v>
       </c>
       <c r="K14" t="n">
-        <v>3.2105</v>
+        <v>12.7629</v>
       </c>
       <c r="L14" t="n">
-        <v>4.9331</v>
+        <v>1.8204</v>
       </c>
       <c r="M14" t="n">
-        <v>-5.5211</v>
+        <v>-10.745</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.5234</v>
+        <v>-11.3224</v>
       </c>
       <c r="O14" t="n">
-        <v>-3.9976</v>
+        <v>0.5773999999999999</v>
       </c>
       <c r="P14" t="n">
-        <v>-2.7029</v>
+        <v>-14.4807</v>
       </c>
       <c r="Q14" t="n">
-        <v>-15.6395</v>
+        <v>-38.2298</v>
       </c>
       <c r="R14" t="n">
-        <v>12.9364</v>
+        <v>23.7487</v>
       </c>
       <c r="S14" t="n">
-        <v>8.984999999999999</v>
+        <v>9.364000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>8.7666</v>
+        <v>5.6057</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2185</v>
+        <v>3.7584</v>
       </c>
       <c r="V14" t="n">
-        <v>-18.5501</v>
+        <v>-12.6018</v>
       </c>
       <c r="W14" t="n">
-        <v>2.0845</v>
+        <v>4.1689</v>
       </c>
       <c r="X14" t="n">
-        <v>-20.6347</v>
+        <v>-16.7708</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. BARBEITO RUIZ</t>
+          <t>J. SANTOLARIA MARTIN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D15" t="n">
-        <v>-14.3891</v>
+        <v>-14.0597</v>
       </c>
       <c r="E15" t="n">
-        <v>-11.228</v>
+        <v>-2.374400000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>-3.161</v>
+        <v>-11.6853</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.6784</v>
+        <v>2.622400000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>4.9278</v>
+        <v>1.6869</v>
       </c>
       <c r="I15" t="n">
-        <v>-6.6059</v>
+        <v>0.9354000000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>3.793</v>
+        <v>8.1434</v>
       </c>
       <c r="K15" t="n">
-        <v>6.385300000000001</v>
+        <v>3.2105</v>
       </c>
       <c r="L15" t="n">
-        <v>-2.5923</v>
+        <v>4.9331</v>
       </c>
       <c r="M15" t="n">
-        <v>-5.471299999999999</v>
+        <v>-5.5211</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.4579</v>
+        <v>-1.5234</v>
       </c>
       <c r="O15" t="n">
-        <v>-4.0136</v>
+        <v>-3.9976</v>
       </c>
       <c r="P15" t="n">
-        <v>2.5098</v>
+        <v>-2.7029</v>
       </c>
       <c r="Q15" t="n">
-        <v>-17.3772</v>
+        <v>-15.6395</v>
       </c>
       <c r="R15" t="n">
-        <v>19.8869</v>
+        <v>12.9364</v>
       </c>
       <c r="S15" t="n">
-        <v>-4.9704</v>
+        <v>4.5711</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.7703</v>
+        <v>3.037</v>
       </c>
       <c r="U15" t="n">
-        <v>-3.2001</v>
+        <v>1.5343</v>
       </c>
       <c r="V15" t="n">
-        <v>-10.2505</v>
+        <v>-18.5501</v>
       </c>
       <c r="W15" t="n">
-        <v>4.1264</v>
+        <v>2.0845</v>
       </c>
       <c r="X15" t="n">
-        <v>-14.3769</v>
+        <v>-20.6347</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P. BALLESPIN DE LA PEÑA</t>
+          <t>G. CAMPOS MARCOS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,76 +1654,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="D16" t="n">
-        <v>-26.4956</v>
+        <v>-18.0401</v>
       </c>
       <c r="E16" t="n">
-        <v>-28.4583</v>
+        <v>-21.2697</v>
       </c>
       <c r="F16" t="n">
-        <v>1.9627</v>
+        <v>3.2295</v>
       </c>
       <c r="G16" t="n">
-        <v>-9.803499999999998</v>
+        <v>5.6708</v>
       </c>
       <c r="H16" t="n">
-        <v>-11.7524</v>
+        <v>0.4592999999999995</v>
       </c>
       <c r="I16" t="n">
-        <v>1.949</v>
+        <v>5.2112</v>
       </c>
       <c r="J16" t="n">
-        <v>-2.209799999999999</v>
+        <v>20.2095</v>
       </c>
       <c r="K16" t="n">
-        <v>-4.571099999999999</v>
+        <v>13.1615</v>
       </c>
       <c r="L16" t="n">
-        <v>2.3611</v>
+        <v>7.048100000000001</v>
       </c>
       <c r="M16" t="n">
-        <v>-7.593599999999999</v>
+        <v>-14.5386</v>
       </c>
       <c r="N16" t="n">
-        <v>-7.1816</v>
+        <v>-12.702</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.4121000000000001</v>
+        <v>-1.8369</v>
       </c>
       <c r="P16" t="n">
-        <v>-19.8871</v>
+        <v>-20.2732</v>
       </c>
       <c r="Q16" t="n">
-        <v>-34.7543</v>
+        <v>-50.3936</v>
       </c>
       <c r="R16" t="n">
-        <v>14.867</v>
+        <v>30.12</v>
       </c>
       <c r="S16" t="n">
-        <v>-2.2342</v>
+        <v>-3.8965</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.2178</v>
+        <v>-3.3924</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.0163</v>
+        <v>-0.504</v>
       </c>
       <c r="V16" t="n">
-        <v>5.4292</v>
+        <v>0.4586999999999999</v>
       </c>
       <c r="W16" t="n">
-        <v>9.7234</v>
+        <v>12.3069</v>
       </c>
       <c r="X16" t="n">
-        <v>-4.2944</v>
+        <v>-11.8481</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. CAMPOS MARCOS</t>
+          <t>P. BALLESPIN DE LA PEÑA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,70 +1732,70 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D17" t="n">
-        <v>-31.9019</v>
+        <v>-21.3445</v>
       </c>
       <c r="E17" t="n">
-        <v>-29.4675</v>
+        <v>-24.7142</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.4346</v>
+        <v>3.3699</v>
       </c>
       <c r="G17" t="n">
-        <v>5.6708</v>
+        <v>-9.803499999999998</v>
       </c>
       <c r="H17" t="n">
-        <v>0.4592999999999995</v>
+        <v>-11.7524</v>
       </c>
       <c r="I17" t="n">
-        <v>5.2112</v>
+        <v>1.949</v>
       </c>
       <c r="J17" t="n">
-        <v>20.2095</v>
+        <v>-2.209799999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>13.1615</v>
+        <v>-4.571099999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>7.048100000000001</v>
+        <v>2.3611</v>
       </c>
       <c r="M17" t="n">
-        <v>-14.5386</v>
+        <v>-7.593599999999999</v>
       </c>
       <c r="N17" t="n">
-        <v>-12.702</v>
+        <v>-7.1816</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.8369</v>
+        <v>-0.4121000000000001</v>
       </c>
       <c r="P17" t="n">
-        <v>-20.2732</v>
+        <v>-19.8871</v>
       </c>
       <c r="Q17" t="n">
-        <v>-50.3936</v>
+        <v>-34.7543</v>
       </c>
       <c r="R17" t="n">
-        <v>30.12</v>
+        <v>14.867</v>
       </c>
       <c r="S17" t="n">
-        <v>-17.7581</v>
+        <v>2.9169</v>
       </c>
       <c r="T17" t="n">
-        <v>-11.5903</v>
+        <v>2.5264</v>
       </c>
       <c r="U17" t="n">
-        <v>-6.1678</v>
+        <v>0.3905999999999999</v>
       </c>
       <c r="V17" t="n">
-        <v>0.4586999999999999</v>
+        <v>5.4292</v>
       </c>
       <c r="W17" t="n">
-        <v>12.3069</v>
+        <v>9.7234</v>
       </c>
       <c r="X17" t="n">
-        <v>-11.8481</v>
+        <v>-4.2944</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>12</v>
       </c>
       <c r="D18" t="n">
-        <v>-33.4661</v>
+        <v>-32.0318</v>
       </c>
       <c r="E18" t="n">
-        <v>-23.5815</v>
+        <v>-22.9469</v>
       </c>
       <c r="F18" t="n">
-        <v>-9.8847</v>
+        <v>-9.0848</v>
       </c>
       <c r="G18" t="n">
         <v>-13.3219</v>
@@ -1858,13 +1858,13 @@
         <v>12.1638</v>
       </c>
       <c r="S18" t="n">
-        <v>-2.9787</v>
+        <v>-1.5444</v>
       </c>
       <c r="T18" t="n">
-        <v>-2.8993</v>
+        <v>-2.2649</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0794999999999999</v>
+        <v>0.7204</v>
       </c>
       <c r="V18" t="n">
         <v>-14.6555</v>
@@ -1891,19 +1891,19 @@
         <v>26</v>
       </c>
       <c r="D19" t="n">
-        <v>-11.22580000000001</v>
+        <v>7.710300000000004</v>
       </c>
       <c r="E19" t="n">
-        <v>-38.9589</v>
+        <v>-33.16430000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>27.7343</v>
+        <v>40.8768</v>
       </c>
       <c r="G19" t="n">
         <v>43.1035</v>
       </c>
       <c r="H19" t="n">
-        <v>-6.214099999999998</v>
+        <v>-6.214099999999999</v>
       </c>
       <c r="I19" t="n">
         <v>49.3169</v>
@@ -1924,10 +1924,10 @@
         <v>-106.0194</v>
       </c>
       <c r="O19" t="n">
-        <v>-48.07639999999999</v>
+        <v>-48.07640000000001</v>
       </c>
       <c r="P19" t="n">
-        <v>-44.40800000000001</v>
+        <v>-44.408</v>
       </c>
       <c r="Q19" t="n">
         <v>-376.5049</v>
@@ -1936,16 +1936,16 @@
         <v>332.0939</v>
       </c>
       <c r="S19" t="n">
-        <v>28.41080000000001</v>
+        <v>47.34520000000001</v>
       </c>
       <c r="T19" t="n">
-        <v>3.082100000000001</v>
+        <v>8.876200000000001</v>
       </c>
       <c r="U19" t="n">
-        <v>25.3293</v>
+        <v>38.47020000000001</v>
       </c>
       <c r="V19" t="n">
-        <v>-38.33110000000001</v>
+        <v>-38.3311</v>
       </c>
       <c r="W19" t="n">
         <v>137.2626</v>
